--- a/figures/figures_data/agingConditionCount.xlsx
+++ b/figures/figures_data/agingConditionCount.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A538"/>
+  <dimension ref="A1:A541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,42 +662,42 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -707,12 +707,12 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -722,12 +722,12 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -737,12 +737,12 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -757,12 +757,12 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -787,12 +787,12 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -822,12 +822,12 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -852,7 +852,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
@@ -862,17 +862,17 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -917,37 +917,37 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105">
@@ -957,32 +957,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="112">
@@ -992,12 +992,12 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -1007,17 +1007,17 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -1117,32 +1117,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144">
@@ -1152,7 +1152,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -1392,17 +1392,17 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="196">
@@ -1412,22 +1412,22 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="201">
@@ -1452,7 +1452,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206">
@@ -1462,7 +1462,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="208">
@@ -1482,42 +1482,42 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="219">
@@ -1542,12 +1542,12 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="225">
@@ -1587,22 +1587,22 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
@@ -1632,7 +1632,7 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242">
@@ -1647,7 +1647,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="245">
@@ -1657,7 +1657,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="247">
@@ -1667,7 +1667,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="249">
@@ -1677,27 +1677,27 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="255">
@@ -1757,12 +1757,12 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="268">
@@ -1772,12 +1772,12 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="271">
@@ -1887,12 +1887,12 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="294">
@@ -1972,12 +1972,12 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="311">
@@ -2257,42 +2257,42 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="374">
@@ -2317,7 +2317,7 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="379">
@@ -2657,7 +2657,7 @@
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="447">
@@ -2672,17 +2672,17 @@
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="452">
@@ -2692,7 +2692,7 @@
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="454">
@@ -3117,6 +3117,21 @@
     </row>
     <row r="538">
       <c r="A538" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="n">
         <v>1</v>
       </c>
     </row>
